--- a/Templates/Template_CKGUmum.xlsx
+++ b/Templates/Template_CKGUmum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lihan\AUTOMATION\AutoCKG\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC587DFB-CA25-48BD-8271-0C7479807D79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A496AE-DBB2-4B2C-858D-DFFD9008899B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -362,7 +362,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
   <si>
     <t>NIK</t>
   </si>
@@ -502,12 +502,6 @@
     <t>Buring</t>
   </si>
   <si>
-    <t>3573031702000003</t>
-  </si>
-  <si>
-    <t>AHMAD DWI CANDRA GUNAWAN</t>
-  </si>
-  <si>
     <t>KH MALIK DALAM 1 RT 1 RW 3 BURING</t>
   </si>
   <si>
@@ -524,6 +518,15 @@
   </si>
   <si>
     <t>tidak tahu</t>
+  </si>
+  <si>
+    <t>6565656565656565</t>
+  </si>
+  <si>
+    <t>INI ADALAH CONTOH</t>
+  </si>
+  <si>
+    <t>HAPUS DAN SESUAIKAN DGN DATA YANG ADA</t>
   </si>
 </sst>
 </file>
@@ -577,12 +580,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -598,13 +607,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -947,11 +963,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.375" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.875" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
@@ -987,7 +1003,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1003,7 +1019,7 @@
         <v>24</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>25</v>
@@ -1050,28 +1066,28 @@
       <c r="V1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="X1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="Y1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="Z1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AA1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AB1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AC1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AD1" s="2" t="s">
         <v>38</v>
       </c>
       <c r="AE1" s="1" t="s">
@@ -1087,95 +1103,100 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:34" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="4" t="str">
+        <f t="shared" ref="C2" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
+        <v>25-05-1970</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <f t="shared" ref="D2" si="1">IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
+        <v>Perempuan</v>
+      </c>
+      <c r="E2" s="4">
+        <v>85230186668</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="M2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2" ca="1" si="0">TEXT(DATE(IF(VALUE(MID(A2,11,2))&lt;=VALUE(RIGHT(YEAR(TODAY()), 2)), 2000+VALUE(MID(A2,11,2)), 1900+VALUE(MID(A2,11,2))), VALUE(MID(A2,9,2)), IF(VALUE(MID(A2,7,2))&gt;40, VALUE(MID(A2,7,2))-40, VALUE(MID(A2,7,2)))), "dd-mm-yyyy")</f>
-        <v>17-02-2000</v>
-      </c>
-      <c r="D2" s="2" t="str">
-        <f t="shared" ref="D2" si="1">IF(A2&lt;&gt;"",IF(VALUE(MID(A2,7,2))&gt;40,"Perempuan","Laki-laki"),"")</f>
-        <v>Laki-laki</v>
-      </c>
-      <c r="E2" s="1">
-        <v>85230186668</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="R2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="U2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Y2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="W2" s="1" t="s">
+      <c r="AA2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AD2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>34</v>
+    </row>
+    <row r="3" spans="1:34" s="4" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
